--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121187717</v>
       </c>
       <c r="B2" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187713</v>
+        <v>121187709</v>
       </c>
       <c r="B3" t="n">
-        <v>105257</v>
+        <v>101250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187709</v>
+        <v>121187713</v>
       </c>
       <c r="B4" t="n">
-        <v>101240</v>
+        <v>105267</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98407</v>
+        <v>98417</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187717</v>
+        <v>121187713</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>105267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187709</v>
+        <v>121187717</v>
       </c>
       <c r="B3" t="n">
-        <v>101250</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187713</v>
+        <v>121187709</v>
       </c>
       <c r="B4" t="n">
-        <v>105267</v>
+        <v>101250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187713</v>
+        <v>121187709</v>
       </c>
       <c r="B2" t="n">
-        <v>105267</v>
+        <v>101263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187717</v>
+        <v>121187713</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>105280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187709</v>
+        <v>121187717</v>
       </c>
       <c r="B4" t="n">
-        <v>101250</v>
+        <v>100360</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98417</v>
+        <v>98430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121187709</v>
       </c>
       <c r="B2" t="n">
-        <v>101263</v>
+        <v>101264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>121187713</v>
       </c>
       <c r="B3" t="n">
-        <v>105280</v>
+        <v>105281</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>121187717</v>
       </c>
       <c r="B4" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98430</v>
+        <v>98431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187709</v>
+        <v>121187713</v>
       </c>
       <c r="B2" t="n">
-        <v>101264</v>
+        <v>105284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187713</v>
+        <v>121187709</v>
       </c>
       <c r="B3" t="n">
-        <v>105281</v>
+        <v>101267</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>121187717</v>
       </c>
       <c r="B4" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
+        <v>98434</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187713</v>
+        <v>121187709</v>
       </c>
       <c r="B2" t="n">
-        <v>105284</v>
+        <v>101267</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187709</v>
+        <v>121187717</v>
       </c>
       <c r="B3" t="n">
-        <v>101267</v>
+        <v>100364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187717</v>
+        <v>121187713</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>105284</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187709</v>
+        <v>121187713</v>
       </c>
       <c r="B2" t="n">
-        <v>101267</v>
+        <v>105290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>221423</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187717</v>
+        <v>121187709</v>
       </c>
       <c r="B3" t="n">
-        <v>100364</v>
+        <v>101273</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187713</v>
+        <v>121187717</v>
       </c>
       <c r="B4" t="n">
-        <v>105284</v>
+        <v>100370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98434</v>
+        <v>98440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>121234577</v>
       </c>
       <c r="B5" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121187713</v>
+        <v>110392682</v>
       </c>
       <c r="B2" t="n">
-        <v>105290</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>1118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Stiftklotterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Opegrapha vermicellifera</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Kunze) J.R.Laundon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+          <t>Svartehatt, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406745</v>
+        <v>406751</v>
       </c>
       <c r="R2" t="n">
-        <v>6204804</v>
+        <v>6204855</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,80 +757,90 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>basaltknalle</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ädellövskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Alex Regnér</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora, Höör socken, 1946-1947</t>
-        </is>
-      </c>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121187709</v>
+        <v>110392549</v>
       </c>
       <c r="B3" t="n">
-        <v>101273</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>1342</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+          <t>Svartehatt, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406745</v>
+        <v>406751</v>
       </c>
       <c r="R3" t="n">
-        <v>6204804</v>
+        <v>6204855</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>Minst två träd (avenbok)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,39 +886,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>basaltknalle</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Ädellövskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>avenbok</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Carpinus betulus</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Alex Regnér</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora, Höör socken, 1946-1947</t>
-        </is>
-      </c>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121187717</v>
+        <v>110392577</v>
       </c>
       <c r="B4" t="n">
-        <v>100370</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +932,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>2604</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+          <t>Svartehatt, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406745</v>
+        <v>406751</v>
       </c>
       <c r="R4" t="n">
-        <v>6204804</v>
+        <v>6204855</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +990,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1947-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,39 +1007,45 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>basaltknalle</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ädellövskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Alex Regnér</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Skånes Flora, Höör socken, 1946-1947</t>
-        </is>
-      </c>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121234577</v>
+        <v>110392607</v>
       </c>
       <c r="B5" t="n">
-        <v>98441</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +1053,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>700 m OSO Sjöhuset, Sk</t>
+          <t>Svartehatt, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406795</v>
+        <v>406751</v>
       </c>
       <c r="R5" t="n">
-        <v>6204938</v>
+        <v>6204855</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,12 +1111,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På lodyta</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,23 +1133,893 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>lövbryn mot väg</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ädellövskog i branter</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Basalt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Basalt # Lodyta på basaltkupp</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110392509</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartehatt, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>406751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6204855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ädellövskog i branter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121234577</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>700 m OSO Sjöhuset, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>406795</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6204938</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lövbryn mot väg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121187709</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>406745</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6204804</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>basaltknalle</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121187713</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>406745</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6204804</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>basaltknalle</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121234368</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartahatt, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>406756</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6204848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>liten basaltknalle i bokskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129363602</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartahatt, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>406746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6204838</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>liten basaltklack i lövskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121187717</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långstorp, 600 m NV, basaltknalle V kraftledningen, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>406745</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6204804</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1947-10-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>basaltknalle</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129361616</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartahatt, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>406746</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6204838</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>liten basaltklack i lövskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60427-2022 artfynd.xlsx
+++ b/artfynd/A 60427-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392549</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,6 +1054,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110392509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121234577</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121187709</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121187713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121234368</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129363602</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121187717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,8 +2080,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129361616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>